--- a/gimnastica/tests/fixtures/inscripcio-nivell-B.xlsx
+++ b/gimnastica/tests/fixtures/inscripcio-nivell-B.xlsx
@@ -3990,7 +3990,11 @@
       <c r="I45" s="169" t="n"/>
       <c r="J45" s="169" t="n"/>
       <c r="K45" s="192" t="n"/>
-      <c r="L45" s="193" t="n"/>
+      <c r="L45" s="193" t="inlineStr">
+        <is>
+          <t>ROCA</t>
+        </is>
+      </c>
       <c r="M45" s="169" t="n"/>
       <c r="N45" s="169" t="n"/>
       <c r="O45" s="169" t="n"/>
